--- a/SQExcel.Portal/src/content/docs/ja/docs/images/inputsheet-data-import/inputsheet-data-import.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/inputsheet-data-import/inputsheet-data-import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\inputsheet-data-import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF93877-D238-4DD5-AA1E-F182B062D5D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEBA664-48D0-473A-B2C2-14DF714C3DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12072" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1110" yWindow="1980" windowWidth="21130" windowHeight="12760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inputsheet-data-export" sheetId="3" r:id="rId1"/>
@@ -1209,8 +1209,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="694765" y="747930"/>
-          <a:ext cx="6096373" cy="5064063"/>
+          <a:off x="691776" y="743448"/>
+          <a:ext cx="6056033" cy="5032687"/>
           <a:chOff x="698500" y="436033"/>
           <a:chExt cx="6146800" cy="4969934"/>
         </a:xfrm>
@@ -3388,226 +3388,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>22412</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>59766</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>205292</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>155014</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="272" name="グループ化 271">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D592D92-BB29-E5C7-93E1-676987C214B1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="255494" y="7984566"/>
-          <a:ext cx="8573845" cy="6621554"/>
-          <a:chOff x="234950" y="6400801"/>
-          <a:chExt cx="8641080" cy="6496049"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="266" name="図 265">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F084645B-F7F8-355B-ACB4-FE34BBA3EF29}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="234950" y="6400801"/>
-            <a:ext cx="8641080" cy="6448303"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="267" name="正方形/長方形 266">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D300EC11-B99A-4FFC-A795-B69A92C44BE4}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5543550" y="12496799"/>
-            <a:ext cx="996950" cy="400051"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="268" name="正方形/長方形 267">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31FC77C3-38A5-4433-97F9-92EF4DAFAF32}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3981450" y="7067550"/>
-            <a:ext cx="4362450" cy="1250950"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="269" name="コネクタ: カギ線 268">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26D16E9E-6245-4675-B883-2BD89611784E}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="268" idx="2"/>
-            <a:endCxn id="267" idx="0"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="5400000">
-            <a:off x="4013201" y="10347324"/>
-            <a:ext cx="4178299" cy="120650"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector3">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val 50000"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:tailEnd type="triangle"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>93</xdr:row>
       <xdr:rowOff>44824</xdr:rowOff>
@@ -3632,7 +3412,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3675,8 +3455,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="233082" y="15683755"/>
-          <a:ext cx="8573845" cy="5377850"/>
+          <a:off x="231588" y="15583649"/>
+          <a:ext cx="8520057" cy="5343485"/>
           <a:chOff x="234950" y="14240437"/>
           <a:chExt cx="8641080" cy="5274756"/>
         </a:xfrm>
@@ -3695,7 +3475,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -3940,7 +3720,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3984,7 +3764,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4028,7 +3808,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4072,7 +3852,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4115,8 +3895,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="233082" y="67899536"/>
-          <a:ext cx="10717306" cy="8311942"/>
+          <a:off x="231588" y="67464747"/>
+          <a:ext cx="10650071" cy="8259649"/>
           <a:chOff x="217714" y="64949614"/>
           <a:chExt cx="10800443" cy="8155060"/>
         </a:xfrm>
@@ -4135,7 +3915,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -4280,8 +4060,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="233082" y="58773040"/>
-          <a:ext cx="10717306" cy="7997138"/>
+          <a:off x="231588" y="58396522"/>
+          <a:ext cx="10650071" cy="7946338"/>
           <a:chOff x="234950" y="56500487"/>
           <a:chExt cx="10801350" cy="7844738"/>
         </a:xfrm>
@@ -4300,7 +4080,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -4558,8 +4338,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="242152" y="77717008"/>
-          <a:ext cx="10714532" cy="6902017"/>
+          <a:off x="240658" y="77219466"/>
+          <a:ext cx="10645802" cy="6857194"/>
           <a:chOff x="226785" y="75309984"/>
           <a:chExt cx="10800443" cy="6767548"/>
         </a:xfrm>
@@ -4578,7 +4358,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -4846,7 +4626,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4889,8 +4669,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9097681" y="1588249"/>
-          <a:ext cx="6099815" cy="3697721"/>
+          <a:off x="9039410" y="1579284"/>
+          <a:ext cx="6060968" cy="3673815"/>
           <a:chOff x="9170519" y="1561355"/>
           <a:chExt cx="6148374" cy="3626328"/>
         </a:xfrm>
@@ -6320,8 +6100,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="18654058" y="1887070"/>
-          <a:ext cx="4202954" cy="5387788"/>
+          <a:off x="18534529" y="1875117"/>
+          <a:ext cx="4176059" cy="5353423"/>
           <a:chOff x="18810940" y="1513541"/>
           <a:chExt cx="4236571" cy="5284693"/>
         </a:xfrm>
@@ -7624,8 +7404,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="251225" y="90051430"/>
-          <a:ext cx="10714532" cy="6896517"/>
+          <a:off x="249731" y="89474701"/>
+          <a:ext cx="10645802" cy="6853188"/>
           <a:chOff x="253093" y="88321242"/>
           <a:chExt cx="10800443" cy="6766529"/>
         </a:xfrm>
@@ -7644,7 +7424,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -7743,8 +7523,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="251225" y="98200242"/>
-          <a:ext cx="10714532" cy="6896519"/>
+          <a:off x="249731" y="97571218"/>
+          <a:ext cx="10645802" cy="6853190"/>
           <a:chOff x="253093" y="96313171"/>
           <a:chExt cx="10800443" cy="6766531"/>
         </a:xfrm>
@@ -7763,7 +7543,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -7833,6 +7613,275 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>22412</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>59766</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>205292</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>155014</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="33" name="グループ化 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADBC742D-95D7-9050-688E-F4C5D3D659F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="254000" y="7933766"/>
+          <a:ext cx="8520057" cy="6579719"/>
+          <a:chOff x="257362" y="7832166"/>
+          <a:chExt cx="8641080" cy="6496048"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="272" name="グループ化 271">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D592D92-BB29-E5C7-93E1-676987C214B1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="257362" y="7832166"/>
+            <a:ext cx="8641080" cy="6496048"/>
+            <a:chOff x="234950" y="6400801"/>
+            <a:chExt cx="8641080" cy="6496049"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="266" name="図 265">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F084645B-F7F8-355B-ACB4-FE34BBA3EF29}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="234950" y="6400801"/>
+              <a:ext cx="8641080" cy="6448303"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="267" name="正方形/長方形 266">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D300EC11-B99A-4FFC-A795-B69A92C44BE4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5543550" y="12496799"/>
+              <a:ext cx="996950" cy="400051"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="268" name="正方形/長方形 267">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31FC77C3-38A5-4433-97F9-92EF4DAFAF32}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3981450" y="7067550"/>
+              <a:ext cx="4362450" cy="1250950"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="269" name="コネクタ: カギ線 268">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26D16E9E-6245-4675-B883-2BD89611784E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="268" idx="2"/>
+              <a:endCxn id="267" idx="0"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm rot="5400000">
+              <a:off x="4013201" y="10347324"/>
+              <a:ext cx="4178299" cy="120650"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector3">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val 50000"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="32" name="図 31">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C36B4B0-7E58-4CDB-B0CA-6B2974CBEC5B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="279773" y="7854577"/>
+            <a:ext cx="252071" cy="225939"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -8103,33 +8152,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247D8D20-CE8B-4D82-A6C6-EA8B8BD03E4C}">
   <dimension ref="B2:CD573"/>
-  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="3" width="3.09765625" style="1"/>
-    <col min="4" max="4" width="34.796875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="24.09765625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="33.296875" style="4" customWidth="1"/>
+    <col min="1" max="3" width="3.08203125" style="1"/>
+    <col min="4" max="4" width="34.83203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="24.08203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="33.33203125" style="4" customWidth="1"/>
     <col min="7" max="7" width="38" style="4" customWidth="1"/>
-    <col min="8" max="8" width="33.296875" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="3.09765625" style="1"/>
+    <col min="8" max="8" width="33.33203125" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="3.08203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:82" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="2:82" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:82" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="2"/>
       <c r="AN3" s="2"/>
       <c r="CD3" s="2"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.55000000000000004">
       <c r="D24" s="4" t="s">
         <v>49</v>
       </c>
@@ -8146,7 +8195,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="36" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:8" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="D25" s="4" t="s">
         <v>54</v>
       </c>
@@ -8163,7 +8212,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:8" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="F26" s="4" t="s">
         <v>57</v>
       </c>
@@ -8174,7 +8223,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="36" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:8" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="D27" s="4" t="s">
         <v>58</v>
       </c>
@@ -8191,7 +8240,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="36" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="F28" s="4" t="s">
         <v>60</v>
       </c>
@@ -8202,7 +8251,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="36" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:8" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="F29" s="4" t="s">
         <v>57</v>
       </c>
@@ -8213,7 +8262,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="36" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:8" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="D30" s="4" t="s">
         <v>64</v>
       </c>
@@ -8230,7 +8279,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="36" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:8" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="F31" s="4" t="s">
         <v>74</v>
       </c>
@@ -8241,7 +8290,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="36" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:8" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="F32" s="4" t="s">
         <v>77</v>
       </c>
@@ -8252,100 +8301,100 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="2"/>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="2"/>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="2"/>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="2"/>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" s="2"/>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B106" s="2"/>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B130" s="2"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B145" s="2"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B164" s="2"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B168" s="2"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B183" s="2"/>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B203" s="2"/>
     </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="222" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B222" s="2"/>
     </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="236" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B236" s="2"/>
     </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="249" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B249" s="2"/>
     </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="258" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B258" s="2"/>
     </row>
-    <row r="277" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="277" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B277" s="2"/>
     </row>
-    <row r="289" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="289" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B289" s="2"/>
     </row>
-    <row r="301" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="301" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B301" s="2"/>
     </row>
-    <row r="330" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="330" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B330" s="2"/>
     </row>
-    <row r="333" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="333" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B333" s="3"/>
     </row>
-    <row r="356" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="356" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B356" s="2"/>
     </row>
-    <row r="365" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="365" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B365" s="2"/>
     </row>
-    <row r="383" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="383" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B383" s="2"/>
     </row>
-    <row r="384" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="384" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B384" s="2"/>
     </row>
-    <row r="410" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="410" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B410" s="2"/>
     </row>
-    <row r="419" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="419" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B419" s="2"/>
     </row>
-    <row r="436" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="436" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B436" s="2"/>
     </row>
-    <row r="469" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="469" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B469" s="2"/>
     </row>
-    <row r="511" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="511" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B511" s="2"/>
     </row>
-    <row r="538" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="538" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B538" s="2"/>
     </row>
-    <row r="573" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="573" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B573" s="2"/>
     </row>
   </sheetData>
@@ -8358,12 +8407,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A29FA320-DA47-41A9-9EA7-7E68689E0E1F}">
   <dimension ref="A1:ED573"/>
-  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="16384" width="3.09765625" style="1"/>
+    <col min="1" max="16384" width="3.08203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:134" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:134" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -8761,7 +8810,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:134" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:134" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -8781,7 +8830,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:134" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:134" x14ac:dyDescent="0.55000000000000004">
       <c r="AN4" s="1" t="s">
         <v>40</v>
       </c>
@@ -8789,7 +8838,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:134" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:134" x14ac:dyDescent="0.55000000000000004">
       <c r="AN5" s="1" t="s">
         <v>37</v>
       </c>
@@ -8797,7 +8846,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:134" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:134" x14ac:dyDescent="0.55000000000000004">
       <c r="AN6" s="1" t="s">
         <v>41</v>
       </c>
@@ -8805,12 +8854,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:134" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:134" x14ac:dyDescent="0.55000000000000004">
       <c r="CD7" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -8818,15 +8867,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="2"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="1" t="s">
         <v>0</v>
       </c>
@@ -8834,20 +8883,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="2"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="1" t="s">
         <v>0</v>
       </c>
@@ -8855,15 +8904,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B106" s="2"/>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="1" t="s">
         <v>0</v>
       </c>
@@ -8871,18 +8920,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B131" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B145" s="2"/>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B164" s="2"/>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="1" t="s">
         <v>0</v>
       </c>
@@ -8890,12 +8939,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B169" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="1" t="s">
         <v>0</v>
       </c>
@@ -8903,20 +8952,20 @@
         <v>12</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B184" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B185" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B203" s="2"/>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" s="1" t="s">
         <v>0</v>
       </c>
@@ -8924,20 +8973,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B223" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B224" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="236" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B236" s="2"/>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="1" t="s">
         <v>0</v>
       </c>
@@ -8945,28 +8994,28 @@
         <v>18</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B250" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B251" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B252" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="258" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B258" s="2"/>
     </row>
-    <row r="277" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="277" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B277" s="2"/>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" s="1" t="s">
         <v>0</v>
       </c>
@@ -8974,20 +9023,20 @@
         <v>21</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B290" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B291" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B301" s="2"/>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A330" s="1" t="s">
         <v>0</v>
       </c>
@@ -8995,25 +9044,25 @@
         <v>25</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B331" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B332" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B333" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B356" s="2"/>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A365" s="1" t="s">
         <v>0</v>
       </c>
@@ -9021,15 +9070,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B366" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B383" s="2"/>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A384" s="1" t="s">
         <v>0</v>
       </c>
@@ -9037,20 +9086,20 @@
         <v>30</v>
       </c>
     </row>
-    <row r="385" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="385" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B385" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="386" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="386" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B386" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="410" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="410" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B410" s="2"/>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A419" s="1" t="s">
         <v>0</v>
       </c>
@@ -9058,29 +9107,29 @@
         <v>33</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B420" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B421" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="436" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="436" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B436" s="2"/>
     </row>
-    <row r="469" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="469" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B469" s="2"/>
     </row>
-    <row r="511" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="511" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B511" s="2"/>
     </row>
-    <row r="538" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="538" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B538" s="2"/>
     </row>
-    <row r="573" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="573" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B573" s="2"/>
     </row>
   </sheetData>
